--- a/files/九龙-旺角-映居.xlsx
+++ b/files/九龙-旺角-映居.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="映居 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="映居" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6298,141 +6336,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>映居 - 映居 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>映居 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>122 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>107 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
-$1,010万
+$1010万
 $29,107/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $976万
@@ -6440,7 +6478,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $930万
@@ -6448,7 +6486,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $935万
@@ -6456,7 +6494,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $790万
@@ -6464,7 +6502,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $935万
@@ -6473,13 +6511,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $937万
@@ -6487,7 +6525,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $802万
@@ -6495,7 +6533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $864万
@@ -6503,7 +6541,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $867万
@@ -6511,7 +6549,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $745万
@@ -6519,7 +6557,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $875万
@@ -6528,13 +6566,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $929万
@@ -6542,7 +6580,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $795万
@@ -6550,7 +6588,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $857万
@@ -6558,7 +6596,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $756万
@@ -6566,7 +6604,7 @@
 (26年-07月)</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $738万
@@ -6574,7 +6612,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $763万
@@ -6583,13 +6621,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $920万
@@ -6597,7 +6635,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $788万
@@ -6605,7 +6643,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $747万
@@ -6613,7 +6651,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $851万
@@ -6621,7 +6659,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $732万
@@ -6629,7 +6667,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $756万
@@ -6638,13 +6676,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $912万
@@ -6652,7 +6690,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $781万
@@ -6660,7 +6698,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $740万
@@ -6668,7 +6706,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $743万
@@ -6676,7 +6714,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $725万
@@ -6684,7 +6722,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $749万
@@ -6693,13 +6731,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $904万
@@ -6707,7 +6745,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $774万
@@ -6715,7 +6753,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $734万
@@ -6723,7 +6761,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $736万
@@ -6731,7 +6769,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $719万
@@ -6739,7 +6777,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $743万
@@ -6748,13 +6786,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $789万
@@ -6762,7 +6800,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $767万
@@ -6770,7 +6808,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $727万
@@ -6778,7 +6816,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $729万
@@ -6786,7 +6824,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $712万
@@ -6794,7 +6832,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $736万
@@ -6803,13 +6841,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $779万
@@ -6817,7 +6855,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $758万
@@ -6825,7 +6863,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $721万
@@ -6833,7 +6871,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $723万
@@ -6841,7 +6879,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $706万
@@ -6849,7 +6887,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $730万
@@ -6858,13 +6896,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $768万
@@ -6872,7 +6910,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $747万
@@ -6880,7 +6918,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $714万
@@ -6888,7 +6926,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $716万
@@ -6896,7 +6934,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $700万
@@ -6904,7 +6942,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $723万
@@ -6913,13 +6951,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $762万
@@ -6927,7 +6965,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $732万
@@ -6935,7 +6973,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $701万
@@ -6943,7 +6981,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $703万
@@ -6951,7 +6989,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $687万
@@ -6959,7 +6997,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $710万
@@ -6968,13 +7006,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $739万
@@ -6982,7 +7020,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $718万
@@ -6990,7 +7028,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $688万
@@ -6998,7 +7036,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $690万
@@ -7006,7 +7044,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $674万
@@ -7014,7 +7052,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $696万
@@ -7023,13 +7061,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $716万
@@ -7037,7 +7075,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $695万
@@ -7045,7 +7083,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $671万
@@ -7053,7 +7091,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $673万
@@ -7061,7 +7099,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $657万
@@ -7069,7 +7107,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $681万
@@ -7078,13 +7116,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $698万
@@ -7092,7 +7130,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $673万
@@ -7100,7 +7138,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $658万
@@ -7108,7 +7146,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $660万
@@ -7116,7 +7154,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $645万
@@ -7124,7 +7162,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $672万
@@ -7133,13 +7171,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $695万
@@ -7147,7 +7185,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $669万
@@ -7155,7 +7193,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $657万
@@ -7163,7 +7201,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $659万
@@ -7171,7 +7209,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $643万
@@ -7179,7 +7217,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $671万
@@ -7188,13 +7226,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $682万
@@ -7202,7 +7240,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $656万
@@ -7210,7 +7248,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $644万
@@ -7218,7 +7256,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $646万
@@ -7226,7 +7264,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $631万
@@ -7234,7 +7272,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $659万
@@ -7243,13 +7281,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $676万
@@ -7257,7 +7295,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $650万
@@ -7265,7 +7303,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $639万
@@ -7273,7 +7311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $640万
@@ -7281,7 +7319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $626万
@@ -7289,7 +7327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $653万
@@ -7298,13 +7336,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $670万
@@ -7312,7 +7350,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $645万
@@ -7320,7 +7358,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $633万
@@ -7328,7 +7366,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $635万
@@ -7336,7 +7374,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $620万
@@ -7344,7 +7382,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $647万
@@ -7353,13 +7391,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $664万
@@ -7367,7 +7405,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $639万
@@ -7375,7 +7413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $627万
@@ -7383,7 +7421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $629万
@@ -7391,7 +7429,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $615万
@@ -7399,7 +7437,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $641万
@@ -7408,13 +7446,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 347呎 (1房)
 $652万
@@ -7422,7 +7460,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 345呎 (1房)
 $628万
@@ -7430,7 +7468,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 338呎 (1房)
 $616万
@@ -7438,7 +7476,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $618万
@@ -7446,7 +7484,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $602万
@@ -7454,7 +7492,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $630万
@@ -7463,15 +7501,15 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr"/>
-      <c r="C25" s="18" t="inlineStr"/>
-      <c r="D25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr"/>
+      <c r="C24" s="22" t="inlineStr"/>
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 343呎 (1房)
 $600万
@@ -7479,7 +7517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 339呎 (1房)
 $602万
@@ -7487,7 +7525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $579万
@@ -7495,7 +7533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $613万
@@ -7504,15 +7542,15 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr"/>
-      <c r="C26" s="18" t="inlineStr"/>
-      <c r="D26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr"/>
+      <c r="C25" s="22" t="inlineStr"/>
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 305呎 (1房)
 $656万
@@ -7520,7 +7558,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 301呎 (1房)
 $664万
@@ -7528,7 +7566,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 343呎 (1房)
 $586万
@@ -7536,7 +7574,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 345呎 (1房)
 $618万
@@ -7547,7 +7585,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/九龙-旺角-映居.xlsx
+++ b/files/九龙-旺角-映居.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -645,9 +645,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -751,6 +775,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>8227736</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>23849</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -786,7 +826,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -797,6 +837,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>6953936</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>20274</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -843,6 +899,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>8229760</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>24277</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -889,6 +961,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8186552</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>24221</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -935,6 +1023,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>8591352</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>24902</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -981,6 +1085,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>8888000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>25614</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1027,6 +1147,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7697272</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>22311</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1062,7 +1198,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1073,6 +1209,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6556000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>19114</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1119,6 +1271,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7627224</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>22499</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1165,6 +1333,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7604608</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>22499</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1200,7 +1384,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1211,6 +1395,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7057336</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>20456</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1257,6 +1457,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8246304</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>23765</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1292,7 +1508,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1303,6 +1519,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6712816</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>19457</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1338,7 +1570,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1349,6 +1581,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6497128</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>18942</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1395,6 +1643,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>6652096</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19623</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1441,6 +1705,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7537640</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>22301</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1476,7 +1756,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1487,6 +1767,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>6994768</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>20275</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1533,6 +1829,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>8172120</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>23551</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1568,7 +1880,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1579,6 +1891,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>6653944</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>19287</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1614,7 +1942,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1625,6 +1953,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>6439136</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>18773</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1671,6 +2015,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>7492320</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>22101</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1706,7 +2066,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1717,6 +2077,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>6573248</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>19447</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1752,7 +2128,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1763,6 +2139,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>6932112</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>20093</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1809,6 +2201,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>8100048</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>23343</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1844,7 +2252,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1855,6 +2263,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>6594104</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>19113</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1890,7 +2314,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1901,6 +2325,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6382024</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>18606</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1936,7 +2376,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1947,6 +2387,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>6534264</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>19275</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1982,7 +2438,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1993,6 +2449,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6515256</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>19276</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2028,7 +2500,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2039,6 +2511,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>6870512</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>19915</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2085,6 +2573,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>8027888</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>23135</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2120,7 +2624,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2131,6 +2635,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>6535232</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>18943</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2166,7 +2686,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2177,6 +2697,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>6324912</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>18440</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2212,7 +2748,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2223,6 +2759,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>6476272</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>19104</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2258,7 +2810,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2269,6 +2821,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>6457176</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>19104</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2304,7 +2872,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2315,6 +2883,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>6809792</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>19739</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2361,6 +2945,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>7955816</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>22927</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2396,7 +2996,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2407,6 +3007,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6477152</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>18774</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2442,7 +3058,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2453,6 +3069,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6268768</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>18276</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2488,7 +3120,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2499,6 +3131,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>6418280</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>18933</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2534,7 +3182,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2545,6 +3193,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>6400152</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>18935</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2580,7 +3244,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2591,6 +3255,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>6749072</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>19563</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2626,7 +3306,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2637,6 +3317,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>6939416</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>19998</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2672,7 +3368,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2683,6 +3379,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>6420040</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>18609</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2718,7 +3430,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2729,6 +3441,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>6213416</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>18115</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2764,7 +3492,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2775,6 +3503,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>6361168</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>18765</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2810,7 +3554,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2821,6 +3565,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>6342952</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>18766</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2856,7 +3616,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2867,6 +3627,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>6666616</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>19324</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2902,7 +3678,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2913,6 +3689,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>6854232</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>19753</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2948,7 +3740,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2959,6 +3751,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6362928</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>18443</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2994,7 +3802,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3005,6 +3813,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>6158152</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>17954</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3040,7 +3864,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3051,6 +3875,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>6304936</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>18599</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3086,7 +3926,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3097,6 +3937,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>6285928</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>18597</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3132,7 +3988,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3143,6 +3999,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>6574128</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>19055</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3178,7 +4050,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3189,6 +4061,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>6759984</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>19481</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3224,7 +4112,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3235,6 +4123,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6244656</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>18100</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3270,7 +4174,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3281,6 +4185,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>6043576</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>17620</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3316,7 +4236,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3327,6 +4247,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6188072</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>18254</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3362,7 +4298,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3373,6 +4309,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>6170120</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>18255</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3408,7 +4360,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3419,6 +4371,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>6442128</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>18673</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3454,7 +4422,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3465,6 +4433,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>6706216</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>19326</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3500,7 +4484,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3511,6 +4495,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>6128320</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>17763</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3546,7 +4546,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3557,6 +4557,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>5931024</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>17292</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3592,7 +4608,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3603,6 +4619,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>6073232</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>17915</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3638,7 +4670,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3649,6 +4681,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6054488</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>17913</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3684,7 +4732,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3695,6 +4743,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>6322096</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>18325</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3730,7 +4794,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3741,6 +4805,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>6499768</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>18731</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3776,7 +4856,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3787,6 +4867,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5993768</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>17373</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3822,7 +4918,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3833,6 +4929,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5781600</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>16856</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3868,7 +4980,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3879,6 +4991,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>5919760</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>17462</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3914,7 +5042,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3925,6 +5053,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5902160</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>17462</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3960,7 +5104,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3971,6 +5115,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>6112568</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>17718</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4006,7 +5166,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4017,6 +5177,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>6305200</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>18171</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4052,7 +5228,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4063,6 +5239,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>5911048</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>17133</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4098,7 +5290,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4109,6 +5301,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5673360</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>16540</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4144,7 +5352,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4155,6 +5363,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5808880</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>17135</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4190,7 +5414,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4201,6 +5425,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5792160</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>17137</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4236,7 +5476,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4247,6 +5487,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5924160</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>17171</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4282,7 +5538,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4293,6 +5549,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>6141608</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>17699</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4328,7 +5600,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4339,6 +5611,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>5907000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>17122</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4374,7 +5662,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4385,6 +5673,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>5660864</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>16504</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4420,7 +5724,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4431,6 +5735,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>5795856</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>17097</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4466,7 +5786,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4477,6 +5797,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>5778168</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>17095</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4512,7 +5848,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4523,6 +5859,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>5886584</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>17063</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4558,7 +5910,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4569,6 +5921,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6112304</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>17615</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4604,7 +5972,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4615,6 +5983,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>5796560</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>16802</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4650,7 +6034,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4661,6 +6045,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5554560</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>16194</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4696,7 +6096,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4707,6 +6107,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>5687440</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>16777</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4742,7 +6158,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4753,6 +6169,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>5670720</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>16777</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4788,7 +6220,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4799,6 +6231,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>5776320</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>16743</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4834,7 +6282,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4845,6 +6293,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>5997200</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>17283</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4880,7 +6344,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4891,6 +6355,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5744728</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>16651</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4926,7 +6406,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4937,6 +6417,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>5505280</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>16050</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4972,7 +6468,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4983,6 +6479,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>5636400</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>16627</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5018,7 +6530,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5029,6 +6541,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>5619680</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>16626</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5064,7 +6592,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5075,6 +6603,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>5724400</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>16592</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5110,7 +6654,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5121,6 +6665,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>5944400</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>17131</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5156,7 +6716,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5167,6 +6727,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>5693688</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>16503</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5202,7 +6778,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5213,6 +6789,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>5456088</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>15907</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5248,7 +6840,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5259,6 +6851,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>5586240</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>16479</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5294,7 +6902,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5305,6 +6913,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>5569520</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>16478</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5340,7 +6964,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5351,6 +6975,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5673360</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>16445</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5386,7 +7026,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5397,6 +7037,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>5891688</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>16979</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5432,7 +7088,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5443,6 +7099,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5643440</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>16358</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5478,7 +7150,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5489,6 +7161,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5407688</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>15766</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5524,7 +7212,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5535,6 +7223,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>5536960</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>16333</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5570,7 +7274,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5581,6 +7285,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>5520240</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>16332</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5616,7 +7336,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5627,6 +7347,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>5623288</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>16299</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5662,7 +7398,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5673,6 +7409,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>5838888</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>16827</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5708,7 +7460,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5719,6 +7471,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>5543208</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>16067</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5754,7 +7522,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5765,6 +7533,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>5298480</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>15447</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5800,7 +7584,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5811,6 +7595,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>5439368</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>16045</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5846,7 +7646,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5857,6 +7657,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>5422648</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>16043</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5892,7 +7708,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5903,6 +7719,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>5523848</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>16011</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5938,7 +7770,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5949,6 +7781,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>5735840</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>16530</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5984,7 +7832,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -5995,6 +7843,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>5398008</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>15646</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6030,7 +7894,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6041,6 +7905,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>5095200</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>14855</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6076,7 +7956,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6087,6 +7967,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>5295840</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>15622</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6122,7 +8018,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6133,6 +8029,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>5278240</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>15388</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6168,7 +8080,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6179,6 +8091,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5435760</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>15756</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6214,7 +8142,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6225,6 +8153,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>5157680</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>15037</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6260,7 +8204,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6271,6 +8215,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5847600</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>19427</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6306,7 +8266,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6317,13 +8277,29 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>5777200</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>18942</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6499,7 +8475,7 @@
           <t>E | 343呎 (1房)
 $790万
 $23,038/呎
-(已售)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -6530,7 +8506,7 @@
           <t>B | 345呎 (1房)
 $802万
 $23,246/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -6554,7 +8530,7 @@
           <t>E | 343呎 (1房)
 $745万
 $21,720/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -6585,7 +8561,7 @@
           <t>B | 345呎 (1房)
 $795万
 $23,039/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6601,7 +8577,7 @@
           <t>D | 339呎 (1房)
 $756万
 $22,299/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -6609,7 +8585,7 @@
           <t>E | 343呎 (1房)
 $738万
 $21,525/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -6617,7 +8593,7 @@
           <t>F | 345呎 (1房)
 $763万
 $22,111/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -6640,7 +8616,7 @@
           <t>B | 345呎 (1房)
 $788万
 $22,833/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -6648,7 +8624,7 @@
           <t>C | 338呎 (1房)
 $747万
 $22,099/呎
-(已售)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -6664,7 +8640,7 @@
           <t>E | 343呎 (1房)
 $732万
 $21,333/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -6672,7 +8648,7 @@
           <t>F | 345呎 (1房)
 $756万
 $21,917/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -6695,7 +8671,7 @@
           <t>B | 345呎 (1房)
 $781万
 $22,630/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -6703,7 +8679,7 @@
           <t>C | 338呎 (1房)
 $740万
 $21,904/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -6711,7 +8687,7 @@
           <t>D | 339呎 (1房)
 $743万
 $21,904/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -6719,7 +8695,7 @@
           <t>E | 343呎 (1房)
 $725万
 $21,144/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -6727,7 +8703,7 @@
           <t>F | 345呎 (1房)
 $749万
 $21,720/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -6750,7 +8726,7 @@
           <t>B | 345呎 (1房)
 $774万
 $22,430/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -6758,7 +8734,7 @@
           <t>C | 338呎 (1房)
 $734万
 $21,709/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -6766,7 +8742,7 @@
           <t>D | 339呎 (1房)
 $736万
 $21,709/呎
-(已售)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -6774,7 +8750,7 @@
           <t>E | 343呎 (1房)
 $719万
 $20,955/呎
-(已售)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -6782,7 +8758,7 @@
           <t>F | 345呎 (1房)
 $743万
 $21,526/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -6797,7 +8773,7 @@
           <t>A | 347呎 (1房)
 $789万
 $22,725/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -6805,7 +8781,7 @@
           <t>B | 345呎 (1房)
 $767万
 $22,230/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -6813,7 +8789,7 @@
           <t>C | 338呎 (1房)
 $727万
 $21,517/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -6821,7 +8797,7 @@
           <t>D | 339呎 (1房)
 $729万
 $21,515/呎
-(已售)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -6829,7 +8805,7 @@
           <t>E | 343呎 (1房)
 $712万
 $20,769/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -6837,7 +8813,7 @@
           <t>F | 345呎 (1房)
 $736万
 $21,334/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -6852,7 +8828,7 @@
           <t>A | 347呎 (1房)
 $779万
 $22,446/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -6860,7 +8836,7 @@
           <t>B | 345呎 (1房)
 $758万
 $21,959/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -6868,7 +8844,7 @@
           <t>C | 338呎 (1房)
 $721万
 $21,325/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -6876,7 +8852,7 @@
           <t>D | 339呎 (1房)
 $723万
 $21,323/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -6884,7 +8860,7 @@
           <t>E | 343呎 (1房)
 $706万
 $20,585/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -6892,7 +8868,7 @@
           <t>F | 345呎 (1房)
 $730万
 $21,146/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -6907,7 +8883,7 @@
           <t>A | 347呎 (1房)
 $768万
 $22,138/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -6915,7 +8891,7 @@
           <t>B | 345呎 (1房)
 $747万
 $21,654/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -6923,7 +8899,7 @@
           <t>C | 338呎 (1房)
 $714万
 $21,133/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -6931,7 +8907,7 @@
           <t>D | 339呎 (1房)
 $716万
 $21,135/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -6939,7 +8915,7 @@
           <t>E | 343呎 (1房)
 $700万
 $20,402/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -6947,7 +8923,7 @@
           <t>F | 345呎 (1房)
 $723万
 $20,958/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -6962,7 +8938,7 @@
           <t>A | 347呎 (1房)
 $762万
 $21,962/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -6970,7 +8946,7 @@
           <t>B | 345呎 (1房)
 $732万
 $21,219/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -6978,7 +8954,7 @@
           <t>C | 338呎 (1房)
 $701万
 $20,744/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -6986,7 +8962,7 @@
           <t>D | 339呎 (1房)
 $703万
 $20,743/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -6994,7 +8970,7 @@
           <t>E | 343呎 (1房)
 $687万
 $20,022/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -7002,7 +8978,7 @@
           <t>F | 345呎 (1房)
 $710万
 $20,569/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -7017,7 +8993,7 @@
           <t>A | 347呎 (1房)
 $739万
 $21,286/呎
-(已售)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -7025,7 +9001,7 @@
           <t>B | 345呎 (1房)
 $718万
 $20,824/呎
-(已售)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -7033,7 +9009,7 @@
           <t>C | 338呎 (1房)
 $688万
 $20,355/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -7041,7 +9017,7 @@
           <t>D | 339呎 (1房)
 $690万
 $20,358/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -7049,7 +9025,7 @@
           <t>E | 343呎 (1房)
 $674万
 $19,650/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -7057,7 +9033,7 @@
           <t>F | 345呎 (1房)
 $696万
 $20,186/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7072,7 +9048,7 @@
           <t>A | 347呎 (1房)
 $716万
 $20,648/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -7080,7 +9056,7 @@
           <t>B | 345呎 (1房)
 $695万
 $20,134/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -7088,7 +9064,7 @@
           <t>C | 338呎 (1房)
 $671万
 $19,843/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -7096,7 +9072,7 @@
           <t>D | 339呎 (1房)
 $673万
 $19,844/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -7104,7 +9080,7 @@
           <t>E | 343呎 (1房)
 $657万
 $19,155/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -7112,7 +9088,7 @@
           <t>F | 345呎 (1房)
 $681万
 $19,742/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -7127,7 +9103,7 @@
           <t>A | 347呎 (1房)
 $698万
 $20,113/呎
-(已售)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -7135,7 +9111,7 @@
           <t>B | 345呎 (1房)
 $673万
 $19,513/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -7143,7 +9119,7 @@
           <t>C | 338呎 (1房)
 $658万
 $19,473/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -7151,7 +9127,7 @@
           <t>D | 339呎 (1房)
 $660万
 $19,472/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -7159,7 +9135,7 @@
           <t>E | 343呎 (1房)
 $645万
 $18,796/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -7167,7 +9143,7 @@
           <t>F | 345呎 (1房)
 $672万
 $19,470/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -7182,7 +9158,7 @@
           <t>A | 347呎 (1房)
 $695万
 $20,017/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -7190,7 +9166,7 @@
           <t>B | 345呎 (1房)
 $669万
 $19,389/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -7198,7 +9174,7 @@
           <t>C | 338呎 (1房)
 $657万
 $19,426/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -7206,7 +9182,7 @@
           <t>D | 339呎 (1房)
 $659万
 $19,428/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -7214,7 +9190,7 @@
           <t>E | 343呎 (1房)
 $643万
 $18,755/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -7222,7 +9198,7 @@
           <t>F | 345呎 (1房)
 $671万
 $19,457/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -7237,7 +9213,7 @@
           <t>A | 347呎 (1房)
 $682万
 $19,640/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -7245,7 +9221,7 @@
           <t>B | 345呎 (1房)
 $656万
 $19,026/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -7253,7 +9229,7 @@
           <t>C | 338呎 (1房)
 $644万
 $19,065/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -7261,7 +9237,7 @@
           <t>D | 339呎 (1房)
 $646万
 $19,065/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -7269,7 +9245,7 @@
           <t>E | 343呎 (1房)
 $631万
 $18,402/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -7277,7 +9253,7 @@
           <t>F | 345呎 (1房)
 $659万
 $19,093/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7292,7 +9268,7 @@
           <t>A | 347呎 (1房)
 $676万
 $19,467/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -7300,7 +9276,7 @@
           <t>B | 345呎 (1房)
 $650万
 $18,855/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -7308,7 +9284,7 @@
           <t>C | 338呎 (1房)
 $639万
 $18,893/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -7316,7 +9292,7 @@
           <t>D | 339呎 (1房)
 $640万
 $18,894/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -7324,7 +9300,7 @@
           <t>E | 343呎 (1房)
 $626万
 $18,239/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -7332,7 +9308,7 @@
           <t>F | 345呎 (1房)
 $653万
 $18,922/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7347,7 +9323,7 @@
           <t>A | 347呎 (1房)
 $670万
 $19,294/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -7355,7 +9331,7 @@
           <t>B | 345呎 (1房)
 $645万
 $18,687/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -7363,7 +9339,7 @@
           <t>C | 338呎 (1房)
 $633万
 $18,725/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -7371,7 +9347,7 @@
           <t>D | 339呎 (1房)
 $635万
 $18,726/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -7379,7 +9355,7 @@
           <t>E | 343呎 (1房)
 $620万
 $18,076/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -7387,7 +9363,7 @@
           <t>F | 345呎 (1房)
 $647万
 $18,754/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7402,7 +9378,7 @@
           <t>A | 347呎 (1房)
 $664万
 $19,121/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -7410,7 +9386,7 @@
           <t>B | 345呎 (1房)
 $639万
 $18,522/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -7418,7 +9394,7 @@
           <t>C | 338呎 (1房)
 $627万
 $18,559/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -7426,7 +9402,7 @@
           <t>D | 339呎 (1房)
 $629万
 $18,560/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -7434,7 +9410,7 @@
           <t>E | 343呎 (1房)
 $615万
 $17,916/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -7442,7 +9418,7 @@
           <t>F | 345呎 (1房)
 $641万
 $18,588/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7457,7 +9433,7 @@
           <t>A | 347呎 (1房)
 $652万
 $18,784/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -7465,7 +9441,7 @@
           <t>B | 345呎 (1房)
 $628万
 $18,194/呎
-(已售)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -7473,7 +9449,7 @@
           <t>C | 338呎 (1房)
 $616万
 $18,231/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -7481,7 +9457,7 @@
           <t>D | 339呎 (1房)
 $618万
 $18,233/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -7489,7 +9465,7 @@
           <t>E | 343呎 (1房)
 $602万
 $17,554/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -7497,7 +9473,7 @@
           <t>F | 345呎 (1房)
 $630万
 $18,258/呎
-(已售)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -7514,7 +9490,7 @@
           <t>C | 343呎 (1房)
 $600万
 $17,487/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -7522,7 +9498,7 @@
           <t>D | 339呎 (1房)
 $602万
 $17,752/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -7530,7 +9506,7 @@
           <t>E | 343呎 (1房)
 $579万
 $16,880/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -7538,7 +9514,7 @@
           <t>F | 345呎 (1房)
 $613万
 $17,780/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7555,7 +9531,7 @@
           <t>C | 305呎 (1房)
 $656万
 $21,525/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -7563,7 +9539,7 @@
           <t>D | 301呎 (1房)
 $664万
 $22,076/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -7571,7 +9547,7 @@
           <t>E | 343呎 (1房)
 $586万
 $17,087/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -7579,7 +9555,7 @@
           <t>F | 345呎 (1房)
 $618万
 $17,904/呎
-(已售)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
